--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:48</t>
+    <t xml:space="preserve">2026-10-05 10:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1060251.62</v>
+        <v>1060251.63</v>
       </c>
     </row>
     <row r="3">
@@ -928,7 +928,7 @@
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>664579.62</v>
+        <v>664579.63</v>
       </c>
     </row>
     <row r="24">
@@ -1013,7 +1013,7 @@
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>629426.12</v>
+        <v>629426.13</v>
       </c>
     </row>
     <row r="29">
